--- a/data/externalStats/File1/RPT_RPT7633743062479QR_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT7633743062479QR_externalStats.xlsx
@@ -2258,7 +2258,7 @@
         <v>11053681.77593989</v>
       </c>
       <c r="AI27" s="56" t="n">
-        <v>14824.51869790835</v>
+        <v>14824.51869790836</v>
       </c>
       <c r="AK27" s="123" t="n">
         <v>3</v>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>5272221.400798335</v>
+        <v>5272221.400798334</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>665.1833099999999</v>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>2098817.353732186</v>
+        <v>2098817.353732187</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>5564.442125</v>
@@ -3694,10 +3694,10 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>51440278.17714211</v>
+        <v>51440278.1771421</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>5712.935709145625</v>
+        <v>5712.935709145626</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -3923,7 +3923,7 @@
         <v>6715.968437806265</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3429.26860315993</v>
+        <v>3429.268603159931</v>
       </c>
       <c r="R53" s="128" t="n">
         <v>822.8623550462368</v>
@@ -3935,13 +3935,13 @@
         <v>10968.09939601243</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>6761.020244310002</v>
+        <v>6761.020244310001</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>3491.421839512038</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>815.5517143006917</v>
+        <v>815.5517143006919</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -4082,7 +4082,7 @@
         <v>22311.02510630787</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>21914.20637614638</v>
+        <v>21914.20637614639</v>
       </c>
       <c r="Q55" s="131" t="n">
         <v>1010.723188589527</v>
@@ -4094,10 +4094,10 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>22987.93657739597</v>
+        <v>22987.93657739599</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>22601.76959326364</v>
+        <v>22601.76959326363</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>1056.466494278384</v>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>23722.9047948107</v>
+        <v>23722.90479481069</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -4229,7 +4229,7 @@
         <v>15561</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6692.3872205212</v>
+        <v>6692.387220521201</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1292.098440020229</v>
@@ -4241,37 +4241,37 @@
         <v>123.8746392546061</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8570.648943562837</v>
+        <v>8570.648943562839</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6842.391992459443</v>
+        <v>6842.391992459445</v>
       </c>
       <c r="Q57" s="131" t="n">
-        <v>1266.647780097429</v>
+        <v>1266.64778009743</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>454.6862978521621</v>
+        <v>454.6862978521622</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>127.6595789522098</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8691.385649361244</v>
+        <v>8691.385649361247</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>7242.965830311594</v>
+        <v>7242.965830311593</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1346.732253058668</v>
+        <v>1346.732253058667</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>469.7823121142044</v>
+        <v>469.7823121142043</v>
       </c>
       <c r="Y57" s="131" t="n">
-        <v>135.7636197204621</v>
+        <v>135.763619720462</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>9195.244015204929</v>
+        <v>9195.244015204928</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -4285,7 +4285,7 @@
         <v>2550857.543178587</v>
       </c>
       <c r="AH57" s="56" t="n">
-        <v>6705.229304216666</v>
+        <v>6705.229304216667</v>
       </c>
     </row>
     <row r="58">
@@ -4403,7 +4403,7 @@
         <v>3533.802715159584</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>3891.914739009913</v>
+        <v>3891.914739009914</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -4427,13 +4427,13 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>454.2017636236161</v>
+        <v>454.2017636236162</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4273.42969397765</v>
+        <v>4273.429693977648</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4727.631457601266</v>
+        <v>4727.631457601264</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -4559,7 +4559,7 @@
         <v>593.9313836793702</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>205.2078727200389</v>
+        <v>205.2078727200388</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>424.0529667237129</v>
@@ -4568,31 +4568,31 @@
         <v>3541.18880143804</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>2424.036978995402</v>
+        <v>2424.036978995403</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>629.7036766255073</v>
+        <v>629.7036766255076</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>213.7944091511753</v>
+        <v>213.7944091511754</v>
       </c>
       <c r="S61" s="131" t="n">
         <v>430.5372579133003</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>3698.072322685386</v>
+        <v>3698.072322685387</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>2543.639495268003</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>670.2012298801745</v>
+        <v>670.2012298801748</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>223.1430582271976</v>
+        <v>223.1430582271975</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>443.9492711165447</v>
+        <v>443.9492711165446</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>3880.933054491919</v>
@@ -4715,46 +4715,46 @@
         <v>6312</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2455.007697092602</v>
+        <v>2455.007697092595</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>425.6162289008444</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>169.5275357149635</v>
+        <v>169.5275357149644</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>7231.577856055945</v>
+        <v>7231.577856055947</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>10281.72931776436</v>
+        <v>10281.72931776435</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2598.534414052418</v>
+        <v>2598.534414052403</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>438.2116805097858</v>
+        <v>438.211680509783</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>179.9999157422485</v>
+        <v>179.999915742249</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>7996.485702050357</v>
+        <v>7996.48570205036</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11213.23171235481</v>
+        <v>11213.23171235479</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2771.892408297972</v>
+        <v>2771.892408297979</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>465.1034039087808</v>
+        <v>465.1034039087781</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>193.1545602542587</v>
+        <v>193.1545602542578</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>8980.645512085166</v>
+        <v>8980.645512085162</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>12410.79588454618</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>7400.058197776589</v>
+        <v>7400.05819777659</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>7400.058197776589</v>
+        <v>7400.05819777659</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -4835,10 +4835,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>8306.118644866136</v>
+        <v>8306.118644866132</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>8306.118644866136</v>
+        <v>8306.118644866132</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -5045,37 +5045,37 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>5930.846562192128</v>
+        <v>5930.846562192127</v>
       </c>
       <c r="K67" s="140" t="n">
         <v>1143.598651544596</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>553.6881347605801</v>
+        <v>553.6881347605803</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>1456.205310819041</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>9084.338659316345</v>
+        <v>9084.338659316343</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>5835.383405729967</v>
+        <v>5835.383405729969</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>1154.261197949845</v>
+        <v>1154.261197949846</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>542.1573693318946</v>
+        <v>542.1573693318948</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>1491.567133808416</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>9023.369106820122</v>
+        <v>9023.369106820126</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>6328.900915682869</v>
+        <v>6328.900915682868</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>1287.413362242337</v>
@@ -5084,7 +5084,7 @@
         <v>560.4309044370964</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>1679.701399547172</v>
+        <v>1679.701399547171</v>
       </c>
       <c r="Z67" s="141" t="n">
         <v>9856.446581909473</v>
@@ -5126,13 +5126,13 @@
         <v>90613</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>45397.3644152249</v>
+        <v>45397.36441522489</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>7816.344192589595</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>2645.420721961224</v>
+        <v>2645.420721961225</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>12769.51348801289</v>
@@ -5147,28 +5147,28 @@
         <v>7928.816126932024</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2678.021513618306</v>
+        <v>2678.021513618307</v>
       </c>
       <c r="S68" s="143" t="n">
         <v>13934.75040705928</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>78272.16785057605</v>
+        <v>78272.16785057608</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>48250.18848713408</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>8317.338582880382</v>
+        <v>8317.338582880378</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2780.933020225742</v>
+        <v>2780.933020225741</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>15513.48949644699</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>83168.06823155333</v>
+        <v>83168.06823155332</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -5182,7 +5182,7 @@
         <v>708217.5836277844</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>493.6664213250516</v>
+        <v>493.6664213250515</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -5336,7 +5336,7 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6151.384466191856</v>
+        <v>6151.384466191857</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1095.863111337395</v>
@@ -5348,13 +5348,13 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7601.026680851134</v>
+        <v>7601.026680851135</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6287.148792283407</v>
+        <v>6287.148792283408</v>
       </c>
       <c r="Q71" s="128" t="n">
-        <v>1133.995088438324</v>
+        <v>1133.995088438323</v>
       </c>
       <c r="R71" s="128" t="n">
         <v>364.6164826990977</v>
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7785.760363420828</v>
+        <v>7785.760363420829</v>
       </c>
       <c r="V71" s="127" t="n">
         <v>6391.704264561599</v>
@@ -5604,19 +5604,19 @@
         <v>828</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7867.39213926166</v>
+        <v>7867.392139261658</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2365.502744595251</v>
+        <v>2365.502744595252</v>
       </c>
       <c r="L75" s="131" t="n">
         <v>540.129599164054</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>90.14648623966944</v>
+        <v>90.14648623966943</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>10863.17096926064</v>
+        <v>10863.17096926063</v>
       </c>
       <c r="P75" s="130" t="n">
         <v>8779.113761857376</v>
@@ -5625,10 +5625,10 @@
         <v>2736.222957408781</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>622.217963822528</v>
+        <v>622.2179638225278</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>97.23255996286009</v>
+        <v>97.23255996286011</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12234.78724305155</v>
@@ -5637,10 +5637,10 @@
         <v>9578.283309154338</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3058.258318549433</v>
+        <v>3058.258318549434</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>690.8187737742181</v>
+        <v>690.8187737742182</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>103.5478408855323</v>
@@ -5872,19 +5872,19 @@
         <v>2351</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>598.5293965081189</v>
+        <v>598.5293965081188</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>24.59313324021368</v>
+        <v>24.59313324021369</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>3.995667682340317</v>
+        <v>3.995667682340316</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>627.1181974306729</v>
+        <v>627.1181974306728</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>740.6706846160412</v>
@@ -5902,7 +5902,7 @@
         <v>804.1565347491608</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>895.7872779917071</v>
+        <v>895.7872779917072</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>77.2441738664258</v>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>993.521855931095</v>
+        <v>993.5218559310953</v>
       </c>
     </row>
     <row r="80">
@@ -6042,13 +6042,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>0</v>
+        <v>7.275957614183426e-12</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.88977869013</v>
       </c>
     </row>
     <row r="82">
@@ -6112,10 +6112,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
     </row>
     <row r="83">
@@ -6559,7 +6559,7 @@
         <v>13003.11723008967</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4563.263691598253</v>
+        <v>4563.263691598255</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1187.478837745334</v>
@@ -6690,7 +6690,7 @@
         <v>22311.02510630787</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>21914.20637614638</v>
+        <v>21914.20637614639</v>
       </c>
       <c r="Q91" s="131" t="n">
         <v>1010.723188589527</v>
@@ -6702,10 +6702,10 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>22987.93657739597</v>
+        <v>22987.93657739599</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>22601.76959326364</v>
+        <v>22601.76959326363</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>1056.466494278384</v>
@@ -6717,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>23722.9047948107</v>
+        <v>23722.90479481069</v>
       </c>
     </row>
     <row r="92">
@@ -6812,7 +6812,7 @@
         <v>14559.77935978286</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3657.60118461548</v>
+        <v>3657.601184615481</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>1002.418242930857</v>
@@ -6845,7 +6845,7 @@
         <v>4404.990571608101</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1160.601085888422</v>
+        <v>1160.601085888423</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>239.3114606059943</v>
@@ -6955,7 +6955,7 @@
         <v>3749.971974583752</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>4108.083998434081</v>
+        <v>4108.083998434082</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -6979,13 +6979,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>454.2017636236161</v>
+        <v>454.2017636236162</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4613.53256034453</v>
+        <v>4613.532560344527</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5067.734323968146</v>
+        <v>5067.734323968143</v>
       </c>
     </row>
     <row r="96">
@@ -7083,7 +7083,7 @@
         <v>618.5245169195839</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>209.2035404023792</v>
+        <v>209.2035404023791</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>424.0529667237129</v>
@@ -7092,10 +7092,10 @@
         <v>4168.306998868713</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>3164.707663611443</v>
+        <v>3164.707663611444</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>680.4674119199826</v>
+        <v>680.4674119199829</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>226.5165239898197</v>
@@ -7104,22 +7104,22 @@
         <v>430.5372579133003</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>4502.228857434546</v>
+        <v>4502.228857434547</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>3439.42677325971</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>747.4454037466003</v>
+        <v>747.4454037466005</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>243.6334623001598</v>
+        <v>243.6334623001597</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>443.9492711165447</v>
+        <v>443.9492711165446</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>4874.454910423014</v>
+        <v>4874.454910423015</v>
       </c>
     </row>
     <row r="98">
@@ -7220,10 +7220,10 @@
         <v>169.5275357149585</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>8691.863841275193</v>
+        <v>8691.863841275195</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11742.0153029836</v>
+        <v>11742.01530298361</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>2598.534414052498</v>
@@ -7232,13 +7232,13 @@
         <v>438.2116805097612</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>179.9999157422426</v>
+        <v>179.9999157422499</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>9596.202553104937</v>
+        <v>9596.20255310494</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>12812.94856340944</v>
+        <v>12812.94856340945</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2771.892408298329</v>
@@ -7247,13 +7247,13 @@
         <v>465.1034039087826</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>193.1545602542537</v>
+        <v>193.154560254261</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>10721.53529077529</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>14151.68566323665</v>
+        <v>14151.68566323666</v>
       </c>
     </row>
     <row r="100">
@@ -7302,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>8999.775048831169</v>
+        <v>8999.77504883117</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>8999.775048831169</v>
+        <v>8999.77504883117</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -7317,10 +7317,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>10047.00842355626</v>
+        <v>10047.00842355625</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>10047.00842355626</v>
+        <v>10047.00842355625</v>
       </c>
     </row>
     <row r="101">
@@ -7522,7 +7522,7 @@
         <v>57887.99439294333</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>3115.375739032019</v>
+        <v>3115.375739032018</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>1430266.310556282</v>
@@ -7571,10 +7571,10 @@
         <v>260672.8335634196</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>60611.41979919453</v>
+        <v>60611.41979919454</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>17205.51634726692</v>
+        <v>17205.51634726693</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>1512829.697999806</v>
@@ -7589,7 +7589,7 @@
         <v>61193.9002771325</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>19133.70432187438</v>
+        <v>19133.70432187437</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>1529759.312411638</v>
@@ -8705,7 +8705,7 @@
         <v>15527606.53524826</v>
       </c>
       <c r="AI26" s="56" t="n">
-        <v>1327.386795179416</v>
+        <v>1327.386795179417</v>
       </c>
       <c r="AK26" s="123" t="n">
         <v>2</v>
@@ -8859,7 +8859,7 @@
         <v>11526956.34609826</v>
       </c>
       <c r="AI28" s="56" t="n">
-        <v>13973.95203328434</v>
+        <v>13973.95203328433</v>
       </c>
       <c r="AK28" s="123" t="n">
         <v>4</v>
@@ -9147,7 +9147,7 @@
         <v>6794400.461363259</v>
       </c>
       <c r="AI32" s="56" t="n">
-        <v>806.0358758925001</v>
+        <v>806.0358758925</v>
       </c>
       <c r="AK32" s="123" t="n">
         <v>8</v>
@@ -9301,7 +9301,7 @@
         <v>5329025.207125469</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>765.0549989487085</v>
+        <v>765.0549989487084</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -10044,7 +10044,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>1625494.155551699</v>
+        <v>1625494.1555517</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>1968.716811057299</v>
@@ -10221,7 +10221,7 @@
         <v>58125289.50454046</v>
       </c>
       <c r="AH49" s="46" t="n">
-        <v>6112.663549744621</v>
+        <v>6112.66354974462</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" thickBot="1">
@@ -10447,7 +10447,7 @@
         <v>6715.968437806265</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3429.26860315993</v>
+        <v>3429.268603159931</v>
       </c>
       <c r="R53" s="128" t="n">
         <v>822.8623550462368</v>
@@ -10459,13 +10459,13 @@
         <v>10968.09939601243</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>6761.020244310002</v>
+        <v>6761.020244310001</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>3491.421839512038</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>815.5517143006917</v>
+        <v>815.5517143006919</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -10606,7 +10606,7 @@
         <v>22311.02510630787</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>21914.20637614638</v>
+        <v>21914.20637614639</v>
       </c>
       <c r="Q55" s="131" t="n">
         <v>1010.723188589527</v>
@@ -10618,10 +10618,10 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>22987.93657739597</v>
+        <v>22987.93657739599</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>22601.76959326364</v>
+        <v>22601.76959326363</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>1056.466494278384</v>
@@ -10633,7 +10633,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>23722.9047948107</v>
+        <v>23722.90479481069</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>2927155.577501255</v>
+        <v>2927155.577501254</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>250.2622030851889</v>
@@ -10753,7 +10753,7 @@
         <v>15561</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6692.3872205212</v>
+        <v>6692.387220521201</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1292.098440020229</v>
@@ -10765,37 +10765,37 @@
         <v>123.8746392546061</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8570.648943562837</v>
+        <v>8570.648943562839</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6842.391992459443</v>
+        <v>6842.391992459445</v>
       </c>
       <c r="Q57" s="131" t="n">
-        <v>1266.647780097429</v>
+        <v>1266.64778009743</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>454.6862978521621</v>
+        <v>454.6862978521622</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>127.6595789522098</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8691.385649361244</v>
+        <v>8691.385649361247</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>7242.965830311594</v>
+        <v>7242.965830311593</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1346.732253058668</v>
+        <v>1346.732253058667</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>469.7823121142044</v>
+        <v>469.7823121142043</v>
       </c>
       <c r="Y57" s="131" t="n">
-        <v>135.7636197204621</v>
+        <v>135.763619720462</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>9195.244015204929</v>
+        <v>9195.244015204928</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -10887,10 +10887,10 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>1945845.153215983</v>
+        <v>1945845.153215984</v>
       </c>
       <c r="AH58" s="56" t="n">
-        <v>6395.623203199999</v>
+        <v>6395.6232032</v>
       </c>
     </row>
     <row r="59">
@@ -10927,7 +10927,7 @@
         <v>3533.802715159584</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>3891.914739009913</v>
+        <v>3891.914739009914</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -10951,13 +10951,13 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>454.2017636236161</v>
+        <v>454.2017636236162</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4273.42969397765</v>
+        <v>4273.429693977648</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4727.631457601266</v>
+        <v>4727.631457601264</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -11083,7 +11083,7 @@
         <v>593.9313836793702</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>205.2078727200389</v>
+        <v>205.2078727200388</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>424.0529667237129</v>
@@ -11092,31 +11092,31 @@
         <v>3541.18880143804</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>2424.036978995402</v>
+        <v>2424.036978995403</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>629.7036766255073</v>
+        <v>629.7036766255076</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>213.7944091511753</v>
+        <v>213.7944091511754</v>
       </c>
       <c r="S61" s="131" t="n">
         <v>430.5372579133003</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>3698.072322685386</v>
+        <v>3698.072322685387</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>2543.639495268003</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>670.2012298801745</v>
+        <v>670.2012298801748</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>223.1430582271976</v>
+        <v>223.1430582271975</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>443.9492711165447</v>
+        <v>443.9492711165446</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>3880.933054491919</v>
@@ -11239,46 +11239,46 @@
         <v>6312</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2455.007697092602</v>
+        <v>2455.007697092595</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>425.6162289008444</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>169.5275357149635</v>
+        <v>169.5275357149644</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>7231.577856055945</v>
+        <v>7231.577856055947</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>10281.72931776436</v>
+        <v>10281.72931776435</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2598.534414052418</v>
+        <v>2598.534414052403</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>438.2116805097858</v>
+        <v>438.211680509783</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>179.9999157422485</v>
+        <v>179.999915742249</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>7996.485702050357</v>
+        <v>7996.48570205036</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11213.23171235481</v>
+        <v>11213.23171235479</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2771.892408297972</v>
+        <v>2771.892408297979</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>465.1034039087808</v>
+        <v>465.1034039087781</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>193.1545602542587</v>
+        <v>193.1545602542578</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>8980.645512085166</v>
+        <v>8980.645512085162</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>12410.79588454618</v>
@@ -11344,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>7400.058197776589</v>
+        <v>7400.05819777659</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>7400.058197776589</v>
+        <v>7400.05819777659</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -11359,10 +11359,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>8306.118644866136</v>
+        <v>8306.118644866132</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>8306.118644866136</v>
+        <v>8306.118644866132</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -11569,37 +11569,37 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>5930.846562192128</v>
+        <v>5930.846562192127</v>
       </c>
       <c r="K67" s="140" t="n">
         <v>1143.598651544596</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>553.6881347605801</v>
+        <v>553.6881347605803</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>1456.205310819041</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>9084.338659316345</v>
+        <v>9084.338659316343</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>5835.383405729967</v>
+        <v>5835.383405729969</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>1154.261197949845</v>
+        <v>1154.261197949846</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>542.1573693318946</v>
+        <v>542.1573693318948</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>1491.567133808416</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>9023.369106820122</v>
+        <v>9023.369106820126</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>6328.900915682869</v>
+        <v>6328.900915682868</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>1287.413362242337</v>
@@ -11608,7 +11608,7 @@
         <v>560.4309044370964</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>1679.701399547172</v>
+        <v>1679.701399547171</v>
       </c>
       <c r="Z67" s="141" t="n">
         <v>9856.446581909473</v>
@@ -11650,13 +11650,13 @@
         <v>90613</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>45397.3644152249</v>
+        <v>45397.36441522489</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>7816.344192589595</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>2645.420721961224</v>
+        <v>2645.420721961225</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>12769.51348801289</v>
@@ -11671,28 +11671,28 @@
         <v>7928.816126932024</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2678.021513618306</v>
+        <v>2678.021513618307</v>
       </c>
       <c r="S68" s="143" t="n">
         <v>13934.75040705928</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>78272.16785057605</v>
+        <v>78272.16785057608</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>48250.18848713408</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>8317.338582880382</v>
+        <v>8317.338582880378</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2780.933020225742</v>
+        <v>2780.933020225741</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>15513.48949644699</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>83168.06823155333</v>
+        <v>83168.06823155332</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -11860,7 +11860,7 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6151.384466191856</v>
+        <v>6151.384466191857</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1095.863111337395</v>
@@ -11872,13 +11872,13 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7601.026680851134</v>
+        <v>7601.026680851135</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6287.148792283407</v>
+        <v>6287.148792283408</v>
       </c>
       <c r="Q71" s="128" t="n">
-        <v>1133.995088438324</v>
+        <v>1133.995088438323</v>
       </c>
       <c r="R71" s="128" t="n">
         <v>364.6164826990977</v>
@@ -11887,7 +11887,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7785.760363420828</v>
+        <v>7785.760363420829</v>
       </c>
       <c r="V71" s="127" t="n">
         <v>6391.704264561599</v>
@@ -12128,19 +12128,19 @@
         <v>828</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7867.39213926166</v>
+        <v>7867.392139261658</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2365.502744595251</v>
+        <v>2365.502744595252</v>
       </c>
       <c r="L75" s="131" t="n">
         <v>540.129599164054</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>90.14648623966944</v>
+        <v>90.14648623966943</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>10863.17096926064</v>
+        <v>10863.17096926063</v>
       </c>
       <c r="P75" s="130" t="n">
         <v>8779.113761857376</v>
@@ -12149,10 +12149,10 @@
         <v>2736.222957408781</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>622.217963822528</v>
+        <v>622.2179638225278</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>97.23255996286009</v>
+        <v>97.23255996286011</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12234.78724305155</v>
@@ -12161,10 +12161,10 @@
         <v>9578.283309154338</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3058.258318549433</v>
+        <v>3058.258318549434</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>690.8187737742181</v>
+        <v>690.8187737742182</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>103.5478408855323</v>
@@ -12396,19 +12396,19 @@
         <v>2351</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>598.5293965081189</v>
+        <v>598.5293965081188</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>24.59313324021368</v>
+        <v>24.59313324021369</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>3.995667682340317</v>
+        <v>3.995667682340316</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>627.1181974306729</v>
+        <v>627.1181974306728</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>740.6706846160412</v>
@@ -12426,7 +12426,7 @@
         <v>804.1565347491608</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>895.7872779917071</v>
+        <v>895.7872779917072</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>77.2441738664258</v>
@@ -12438,7 +12438,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>993.521855931095</v>
+        <v>993.5218559310953</v>
       </c>
     </row>
     <row r="80">
@@ -12566,13 +12566,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>0</v>
+        <v>7.275957614183426e-12</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.88977869013</v>
       </c>
     </row>
     <row r="82">
@@ -12636,10 +12636,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
     </row>
     <row r="83">
@@ -13083,7 +13083,7 @@
         <v>13003.11723008967</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4563.263691598253</v>
+        <v>4563.263691598255</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1187.478837745334</v>
@@ -13214,7 +13214,7 @@
         <v>22311.02510630787</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>21914.20637614638</v>
+        <v>21914.20637614639</v>
       </c>
       <c r="Q91" s="131" t="n">
         <v>1010.723188589527</v>
@@ -13226,10 +13226,10 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>22987.93657739597</v>
+        <v>22987.93657739599</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>22601.76959326364</v>
+        <v>22601.76959326363</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>1056.466494278384</v>
@@ -13241,7 +13241,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>23722.9047948107</v>
+        <v>23722.90479481069</v>
       </c>
     </row>
     <row r="92">
@@ -13336,7 +13336,7 @@
         <v>14559.77935978286</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3657.60118461548</v>
+        <v>3657.601184615481</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>1002.418242930857</v>
@@ -13369,7 +13369,7 @@
         <v>4404.990571608101</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1160.601085888422</v>
+        <v>1160.601085888423</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>239.3114606059943</v>
@@ -13479,7 +13479,7 @@
         <v>3749.971974583752</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>4108.083998434081</v>
+        <v>4108.083998434082</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -13503,13 +13503,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>454.2017636236161</v>
+        <v>454.2017636236162</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4613.53256034453</v>
+        <v>4613.532560344527</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5067.734323968146</v>
+        <v>5067.734323968143</v>
       </c>
     </row>
     <row r="96">
@@ -13607,7 +13607,7 @@
         <v>618.5245169195839</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>209.2035404023792</v>
+        <v>209.2035404023791</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>424.0529667237129</v>
@@ -13616,10 +13616,10 @@
         <v>4168.306998868713</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>3164.707663611443</v>
+        <v>3164.707663611444</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>680.4674119199826</v>
+        <v>680.4674119199829</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>226.5165239898197</v>
@@ -13628,22 +13628,22 @@
         <v>430.5372579133003</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>4502.228857434546</v>
+        <v>4502.228857434547</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>3439.42677325971</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>747.4454037466003</v>
+        <v>747.4454037466005</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>243.6334623001598</v>
+        <v>243.6334623001597</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>443.9492711165447</v>
+        <v>443.9492711165446</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>4874.454910423014</v>
+        <v>4874.454910423015</v>
       </c>
     </row>
     <row r="98">
@@ -13744,10 +13744,10 @@
         <v>169.5275357149585</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>8691.863841275193</v>
+        <v>8691.863841275195</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11742.0153029836</v>
+        <v>11742.01530298361</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>2598.534414052498</v>
@@ -13756,13 +13756,13 @@
         <v>438.2116805097612</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>179.9999157422426</v>
+        <v>179.9999157422499</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>9596.202553104937</v>
+        <v>9596.20255310494</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>12812.94856340944</v>
+        <v>12812.94856340945</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2771.892408298329</v>
@@ -13771,13 +13771,13 @@
         <v>465.1034039087826</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>193.1545602542537</v>
+        <v>193.154560254261</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>10721.53529077529</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>14151.68566323665</v>
+        <v>14151.68566323666</v>
       </c>
     </row>
     <row r="100">
@@ -13826,10 +13826,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>8999.775048831169</v>
+        <v>8999.77504883117</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>8999.775048831169</v>
+        <v>8999.77504883117</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -13841,10 +13841,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>10047.00842355626</v>
+        <v>10047.00842355625</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>10047.00842355626</v>
+        <v>10047.00842355625</v>
       </c>
     </row>
     <row r="101">
@@ -14046,7 +14046,7 @@
         <v>57887.99439294333</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>3115.375739032019</v>
+        <v>3115.375739032018</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>1430266.310556282</v>
@@ -14095,10 +14095,10 @@
         <v>260672.8335634196</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>60611.41979919453</v>
+        <v>60611.41979919454</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>17205.51634726692</v>
+        <v>17205.51634726693</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>1512829.697999806</v>
@@ -14113,7 +14113,7 @@
         <v>61193.9002771325</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>19133.70432187438</v>
+        <v>19133.70432187437</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>1529759.312411638</v>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>11115569.71666374</v>
+        <v>11115569.71666375</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>13662.27643199234</v>
@@ -15825,7 +15825,7 @@
         <v>5790446.392228267</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>785.5461680356123</v>
+        <v>785.5461680356124</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -16196,7 +16196,7 @@
         <v>2565277.66149139</v>
       </c>
       <c r="AI39" s="56" t="n">
-        <v>8051.17770688</v>
+        <v>8051.177706879998</v>
       </c>
       <c r="AK39" s="123" t="n">
         <v>15</v>
@@ -16494,7 +16494,7 @@
         <v>1840597.694286198</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>3412.859287341889</v>
+        <v>3412.859287341888</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -16971,7 +16971,7 @@
         <v>6715.968437806265</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3429.26860315993</v>
+        <v>3429.268603159931</v>
       </c>
       <c r="R53" s="128" t="n">
         <v>822.8623550462368</v>
@@ -16983,13 +16983,13 @@
         <v>10968.09939601243</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>6761.020244310002</v>
+        <v>6761.020244310001</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>3491.421839512038</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>815.5517143006917</v>
+        <v>815.5517143006919</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -17130,7 +17130,7 @@
         <v>22311.02510630787</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>21914.20637614638</v>
+        <v>21914.20637614639</v>
       </c>
       <c r="Q55" s="131" t="n">
         <v>1010.723188589527</v>
@@ -17142,10 +17142,10 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>22987.93657739597</v>
+        <v>22987.93657739599</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>22601.76959326364</v>
+        <v>22601.76959326363</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>1056.466494278384</v>
@@ -17157,7 +17157,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>23722.9047948107</v>
+        <v>23722.90479481069</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -17277,7 +17277,7 @@
         <v>15561</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6692.3872205212</v>
+        <v>6692.387220521201</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1292.098440020229</v>
@@ -17289,37 +17289,37 @@
         <v>123.8746392546061</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8570.648943562837</v>
+        <v>8570.648943562839</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6842.391992459443</v>
+        <v>6842.391992459445</v>
       </c>
       <c r="Q57" s="131" t="n">
-        <v>1266.647780097429</v>
+        <v>1266.64778009743</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>454.6862978521621</v>
+        <v>454.6862978521622</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>127.6595789522098</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8691.385649361244</v>
+        <v>8691.385649361247</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>7242.965830311594</v>
+        <v>7242.965830311593</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1346.732253058668</v>
+        <v>1346.732253058667</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>469.7823121142044</v>
+        <v>469.7823121142043</v>
       </c>
       <c r="Y57" s="131" t="n">
-        <v>135.7636197204621</v>
+        <v>135.763619720462</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>9195.244015204929</v>
+        <v>9195.244015204928</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -17451,7 +17451,7 @@
         <v>3533.802715159584</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>3891.914739009913</v>
+        <v>3891.914739009914</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -17475,13 +17475,13 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>454.2017636236161</v>
+        <v>454.2017636236162</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4273.42969397765</v>
+        <v>4273.429693977648</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4727.631457601266</v>
+        <v>4727.631457601264</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -17607,7 +17607,7 @@
         <v>593.9313836793702</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>205.2078727200389</v>
+        <v>205.2078727200388</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>424.0529667237129</v>
@@ -17616,31 +17616,31 @@
         <v>3541.18880143804</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>2424.036978995402</v>
+        <v>2424.036978995403</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>629.7036766255073</v>
+        <v>629.7036766255076</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>213.7944091511753</v>
+        <v>213.7944091511754</v>
       </c>
       <c r="S61" s="131" t="n">
         <v>430.5372579133003</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>3698.072322685386</v>
+        <v>3698.072322685387</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>2543.639495268003</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>670.2012298801745</v>
+        <v>670.2012298801748</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>223.1430582271976</v>
+        <v>223.1430582271975</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>443.9492711165447</v>
+        <v>443.9492711165446</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>3880.933054491919</v>
@@ -17657,7 +17657,7 @@
         <v>1201473.610378417</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>203.9872088689193</v>
+        <v>203.9872088689194</v>
       </c>
     </row>
     <row r="62">
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="AG62" s="122" t="n">
-        <v>1076065.182731766</v>
+        <v>1076065.182731765</v>
       </c>
       <c r="AH62" s="56" t="n">
         <v>4715.065128560274</v>
@@ -17763,46 +17763,46 @@
         <v>6312</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2455.007697092602</v>
+        <v>2455.007697092595</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>425.6162289008444</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>169.5275357149635</v>
+        <v>169.5275357149644</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>7231.577856055945</v>
+        <v>7231.577856055947</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>10281.72931776436</v>
+        <v>10281.72931776435</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2598.534414052418</v>
+        <v>2598.534414052403</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>438.2116805097858</v>
+        <v>438.211680509783</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>179.9999157422485</v>
+        <v>179.999915742249</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>7996.485702050357</v>
+        <v>7996.48570205036</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11213.23171235481</v>
+        <v>11213.23171235479</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2771.892408297972</v>
+        <v>2771.892408297979</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>465.1034039087808</v>
+        <v>465.1034039087781</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>193.1545602542587</v>
+        <v>193.1545602542578</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>8980.645512085166</v>
+        <v>8980.645512085162</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>12410.79588454618</v>
@@ -17868,10 +17868,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>7400.058197776589</v>
+        <v>7400.05819777659</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>7400.058197776589</v>
+        <v>7400.05819777659</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -17883,10 +17883,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>8306.118644866136</v>
+        <v>8306.118644866132</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>8306.118644866136</v>
+        <v>8306.118644866132</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -17983,7 +17983,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>830147.971541152</v>
+        <v>830147.9715411521</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>524.462996491248</v>
@@ -18093,37 +18093,37 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>5930.846562192128</v>
+        <v>5930.846562192127</v>
       </c>
       <c r="K67" s="140" t="n">
         <v>1143.598651544596</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>553.6881347605801</v>
+        <v>553.6881347605803</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>1456.205310819041</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>9084.338659316345</v>
+        <v>9084.338659316343</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>5835.383405729967</v>
+        <v>5835.383405729969</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>1154.261197949845</v>
+        <v>1154.261197949846</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>542.1573693318946</v>
+        <v>542.1573693318948</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>1491.567133808416</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>9023.369106820122</v>
+        <v>9023.369106820126</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>6328.900915682869</v>
+        <v>6328.900915682868</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>1287.413362242337</v>
@@ -18132,7 +18132,7 @@
         <v>560.4309044370964</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>1679.701399547172</v>
+        <v>1679.701399547171</v>
       </c>
       <c r="Z67" s="141" t="n">
         <v>9856.446581909473</v>
@@ -18174,13 +18174,13 @@
         <v>90613</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>45397.3644152249</v>
+        <v>45397.36441522489</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>7816.344192589595</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>2645.420721961224</v>
+        <v>2645.420721961225</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>12769.51348801289</v>
@@ -18195,28 +18195,28 @@
         <v>7928.816126932024</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2678.021513618306</v>
+        <v>2678.021513618307</v>
       </c>
       <c r="S68" s="143" t="n">
         <v>13934.75040705928</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>78272.16785057605</v>
+        <v>78272.16785057608</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>48250.18848713408</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>8317.338582880382</v>
+        <v>8317.338582880378</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2780.933020225742</v>
+        <v>2780.933020225741</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>15513.48949644699</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>83168.06823155333</v>
+        <v>83168.06823155332</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -18384,7 +18384,7 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6151.384466191856</v>
+        <v>6151.384466191857</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1095.863111337395</v>
@@ -18396,13 +18396,13 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7601.026680851134</v>
+        <v>7601.026680851135</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6287.148792283407</v>
+        <v>6287.148792283408</v>
       </c>
       <c r="Q71" s="128" t="n">
-        <v>1133.995088438324</v>
+        <v>1133.995088438323</v>
       </c>
       <c r="R71" s="128" t="n">
         <v>364.6164826990977</v>
@@ -18411,7 +18411,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7785.760363420828</v>
+        <v>7785.760363420829</v>
       </c>
       <c r="V71" s="127" t="n">
         <v>6391.704264561599</v>
@@ -18652,19 +18652,19 @@
         <v>828</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7867.39213926166</v>
+        <v>7867.392139261658</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2365.502744595251</v>
+        <v>2365.502744595252</v>
       </c>
       <c r="L75" s="131" t="n">
         <v>540.129599164054</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>90.14648623966944</v>
+        <v>90.14648623966943</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>10863.17096926064</v>
+        <v>10863.17096926063</v>
       </c>
       <c r="P75" s="130" t="n">
         <v>8779.113761857376</v>
@@ -18673,10 +18673,10 @@
         <v>2736.222957408781</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>622.217963822528</v>
+        <v>622.2179638225278</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>97.23255996286009</v>
+        <v>97.23255996286011</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12234.78724305155</v>
@@ -18685,10 +18685,10 @@
         <v>9578.283309154338</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3058.258318549433</v>
+        <v>3058.258318549434</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>690.8187737742181</v>
+        <v>690.8187737742182</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>103.5478408855323</v>
@@ -18920,19 +18920,19 @@
         <v>2351</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>598.5293965081189</v>
+        <v>598.5293965081188</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>24.59313324021368</v>
+        <v>24.59313324021369</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>3.995667682340317</v>
+        <v>3.995667682340316</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>627.1181974306729</v>
+        <v>627.1181974306728</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>740.6706846160412</v>
@@ -18950,7 +18950,7 @@
         <v>804.1565347491608</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>895.7872779917071</v>
+        <v>895.7872779917072</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>77.2441738664258</v>
@@ -18962,7 +18962,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>993.521855931095</v>
+        <v>993.5218559310953</v>
       </c>
     </row>
     <row r="80">
@@ -19090,13 +19090,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>0</v>
+        <v>7.275957614183426e-12</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.88977869013</v>
       </c>
     </row>
     <row r="82">
@@ -19160,10 +19160,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
     </row>
     <row r="83">
@@ -19607,7 +19607,7 @@
         <v>13003.11723008967</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4563.263691598253</v>
+        <v>4563.263691598255</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1187.478837745334</v>
@@ -19738,7 +19738,7 @@
         <v>22311.02510630787</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>21914.20637614638</v>
+        <v>21914.20637614639</v>
       </c>
       <c r="Q91" s="131" t="n">
         <v>1010.723188589527</v>
@@ -19750,10 +19750,10 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>22987.93657739597</v>
+        <v>22987.93657739599</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>22601.76959326364</v>
+        <v>22601.76959326363</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>1056.466494278384</v>
@@ -19765,7 +19765,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>23722.9047948107</v>
+        <v>23722.90479481069</v>
       </c>
     </row>
     <row r="92">
@@ -19860,7 +19860,7 @@
         <v>14559.77935978286</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3657.60118461548</v>
+        <v>3657.601184615481</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>1002.418242930857</v>
@@ -19893,7 +19893,7 @@
         <v>4404.990571608101</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1160.601085888422</v>
+        <v>1160.601085888423</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>239.3114606059943</v>
@@ -20003,7 +20003,7 @@
         <v>3749.971974583752</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>4108.083998434081</v>
+        <v>4108.083998434082</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -20027,13 +20027,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>454.2017636236161</v>
+        <v>454.2017636236162</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4613.53256034453</v>
+        <v>4613.532560344527</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5067.734323968146</v>
+        <v>5067.734323968143</v>
       </c>
     </row>
     <row r="96">
@@ -20131,7 +20131,7 @@
         <v>618.5245169195839</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>209.2035404023792</v>
+        <v>209.2035404023791</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>424.0529667237129</v>
@@ -20140,10 +20140,10 @@
         <v>4168.306998868713</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>3164.707663611443</v>
+        <v>3164.707663611444</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>680.4674119199826</v>
+        <v>680.4674119199829</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>226.5165239898197</v>
@@ -20152,22 +20152,22 @@
         <v>430.5372579133003</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>4502.228857434546</v>
+        <v>4502.228857434547</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>3439.42677325971</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>747.4454037466003</v>
+        <v>747.4454037466005</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>243.6334623001598</v>
+        <v>243.6334623001597</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>443.9492711165447</v>
+        <v>443.9492711165446</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>4874.454910423014</v>
+        <v>4874.454910423015</v>
       </c>
     </row>
     <row r="98">
@@ -20268,10 +20268,10 @@
         <v>169.5275357149585</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>8691.863841275193</v>
+        <v>8691.863841275195</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11742.0153029836</v>
+        <v>11742.01530298361</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>2598.534414052498</v>
@@ -20280,13 +20280,13 @@
         <v>438.2116805097612</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>179.9999157422426</v>
+        <v>179.9999157422499</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>9596.202553104937</v>
+        <v>9596.20255310494</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>12812.94856340944</v>
+        <v>12812.94856340945</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2771.892408298329</v>
@@ -20295,13 +20295,13 @@
         <v>465.1034039087826</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>193.1545602542537</v>
+        <v>193.154560254261</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>10721.53529077529</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>14151.68566323665</v>
+        <v>14151.68566323666</v>
       </c>
     </row>
     <row r="100">
@@ -20350,10 +20350,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>8999.775048831169</v>
+        <v>8999.77504883117</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>8999.775048831169</v>
+        <v>8999.77504883117</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -20365,10 +20365,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>10047.00842355626</v>
+        <v>10047.00842355625</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>10047.00842355626</v>
+        <v>10047.00842355625</v>
       </c>
     </row>
     <row r="101">
@@ -20570,7 +20570,7 @@
         <v>57887.99439294333</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>3115.375739032019</v>
+        <v>3115.375739032018</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>1430266.310556282</v>
@@ -20619,10 +20619,10 @@
         <v>260672.8335634196</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>60611.41979919453</v>
+        <v>60611.41979919454</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>17205.51634726692</v>
+        <v>17205.51634726693</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>1512829.697999806</v>
@@ -20637,7 +20637,7 @@
         <v>61193.9002771325</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>19133.70432187438</v>
+        <v>19133.70432187437</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>1529759.312411638</v>
@@ -21676,7 +21676,7 @@
         <v>55708663.09676258</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>68660.92484379244</v>
+        <v>68660.92484379245</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -22124,7 +22124,7 @@
         <v>11120783.40219731</v>
       </c>
       <c r="AI31" s="56" t="n">
-        <v>13115.78537471264</v>
+        <v>13115.78537471265</v>
       </c>
       <c r="AK31" s="123" t="n">
         <v>7</v>
@@ -22272,7 +22272,7 @@
         <v>6216688.07726003</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>801.3791921122272</v>
+        <v>801.3791921122273</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -22938,10 +22938,10 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>2006758.971569033</v>
+        <v>2006758.971569034</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>3570.123843302602</v>
+        <v>3570.123843302601</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -23495,7 +23495,7 @@
         <v>6715.968437806265</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3429.26860315993</v>
+        <v>3429.268603159931</v>
       </c>
       <c r="R53" s="128" t="n">
         <v>822.8623550462368</v>
@@ -23507,13 +23507,13 @@
         <v>10968.09939601243</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>6761.020244310002</v>
+        <v>6761.020244310001</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>3491.421839512038</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>815.5517143006917</v>
+        <v>815.5517143006919</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>9810448.624385366</v>
+        <v>9810448.624385368</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>19437.61626146535</v>
@@ -23654,7 +23654,7 @@
         <v>22311.02510630787</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>21914.20637614638</v>
+        <v>21914.20637614639</v>
       </c>
       <c r="Q55" s="131" t="n">
         <v>1010.723188589527</v>
@@ -23666,10 +23666,10 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>22987.93657739597</v>
+        <v>22987.93657739599</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>22601.76959326364</v>
+        <v>22601.76959326363</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>1056.466494278384</v>
@@ -23681,7 +23681,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>23722.9047948107</v>
+        <v>23722.90479481069</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -23801,7 +23801,7 @@
         <v>15561</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6692.3872205212</v>
+        <v>6692.387220521201</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1292.098440020229</v>
@@ -23813,37 +23813,37 @@
         <v>123.8746392546061</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8570.648943562837</v>
+        <v>8570.648943562839</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6842.391992459443</v>
+        <v>6842.391992459445</v>
       </c>
       <c r="Q57" s="131" t="n">
-        <v>1266.647780097429</v>
+        <v>1266.64778009743</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>454.6862978521621</v>
+        <v>454.6862978521622</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>127.6595789522098</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8691.385649361244</v>
+        <v>8691.385649361247</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>7242.965830311594</v>
+        <v>7242.965830311593</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1346.732253058668</v>
+        <v>1346.732253058667</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>469.7823121142044</v>
+        <v>469.7823121142043</v>
       </c>
       <c r="Y57" s="131" t="n">
-        <v>135.7636197204621</v>
+        <v>135.763619720462</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>9195.244015204929</v>
+        <v>9195.244015204928</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -23854,7 +23854,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>3177826.490204261</v>
+        <v>3177826.49020426</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>251.5675531601408</v>
@@ -23975,7 +23975,7 @@
         <v>3533.802715159584</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>3891.914739009913</v>
+        <v>3891.914739009914</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -23999,13 +23999,13 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>454.2017636236161</v>
+        <v>454.2017636236162</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4273.42969397765</v>
+        <v>4273.429693977648</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4727.631457601266</v>
+        <v>4727.631457601264</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -24131,7 +24131,7 @@
         <v>593.9313836793702</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>205.2078727200389</v>
+        <v>205.2078727200388</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>424.0529667237129</v>
@@ -24140,31 +24140,31 @@
         <v>3541.18880143804</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>2424.036978995402</v>
+        <v>2424.036978995403</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>629.7036766255073</v>
+        <v>629.7036766255076</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>213.7944091511753</v>
+        <v>213.7944091511754</v>
       </c>
       <c r="S61" s="131" t="n">
         <v>430.5372579133003</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>3698.072322685386</v>
+        <v>3698.072322685387</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>2543.639495268003</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>670.2012298801745</v>
+        <v>670.2012298801748</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>223.1430582271976</v>
+        <v>223.1430582271975</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>443.9492711165447</v>
+        <v>443.9492711165446</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>3880.933054491919</v>
@@ -24287,46 +24287,46 @@
         <v>6312</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2455.007697092602</v>
+        <v>2455.007697092595</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>425.6162289008444</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>169.5275357149635</v>
+        <v>169.5275357149644</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>7231.577856055945</v>
+        <v>7231.577856055947</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>10281.72931776436</v>
+        <v>10281.72931776435</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2598.534414052418</v>
+        <v>2598.534414052403</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>438.2116805097858</v>
+        <v>438.211680509783</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>179.9999157422485</v>
+        <v>179.999915742249</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>7996.485702050357</v>
+        <v>7996.48570205036</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11213.23171235481</v>
+        <v>11213.23171235479</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2771.892408297972</v>
+        <v>2771.892408297979</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>465.1034039087808</v>
+        <v>465.1034039087781</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>193.1545602542587</v>
+        <v>193.1545602542578</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>8980.645512085166</v>
+        <v>8980.645512085162</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>12410.79588454618</v>
@@ -24392,10 +24392,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>7400.058197776589</v>
+        <v>7400.05819777659</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>7400.058197776589</v>
+        <v>7400.05819777659</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -24407,10 +24407,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>8306.118644866136</v>
+        <v>8306.118644866132</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>8306.118644866136</v>
+        <v>8306.118644866132</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -24617,37 +24617,37 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>5930.846562192128</v>
+        <v>5930.846562192127</v>
       </c>
       <c r="K67" s="140" t="n">
         <v>1143.598651544596</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>553.6881347605801</v>
+        <v>553.6881347605803</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>1456.205310819041</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>9084.338659316345</v>
+        <v>9084.338659316343</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>5835.383405729967</v>
+        <v>5835.383405729969</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>1154.261197949845</v>
+        <v>1154.261197949846</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>542.1573693318946</v>
+        <v>542.1573693318948</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>1491.567133808416</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>9023.369106820122</v>
+        <v>9023.369106820126</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>6328.900915682869</v>
+        <v>6328.900915682868</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>1287.413362242337</v>
@@ -24656,7 +24656,7 @@
         <v>560.4309044370964</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>1679.701399547172</v>
+        <v>1679.701399547171</v>
       </c>
       <c r="Z67" s="141" t="n">
         <v>9856.446581909473</v>
@@ -24698,13 +24698,13 @@
         <v>90613</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>45397.3644152249</v>
+        <v>45397.36441522489</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>7816.344192589595</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>2645.420721961224</v>
+        <v>2645.420721961225</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>12769.51348801289</v>
@@ -24719,28 +24719,28 @@
         <v>7928.816126932024</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2678.021513618306</v>
+        <v>2678.021513618307</v>
       </c>
       <c r="S68" s="143" t="n">
         <v>13934.75040705928</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>78272.16785057605</v>
+        <v>78272.16785057608</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>48250.18848713408</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>8317.338582880382</v>
+        <v>8317.338582880378</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2780.933020225742</v>
+        <v>2780.933020225741</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>15513.48949644699</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>83168.06823155333</v>
+        <v>83168.06823155332</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -24754,7 +24754,7 @@
         <v>408013.1720265263</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>730.5517633907934</v>
+        <v>730.5517633907933</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -24908,7 +24908,7 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6151.384466191856</v>
+        <v>6151.384466191857</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1095.863111337395</v>
@@ -24920,13 +24920,13 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7601.026680851134</v>
+        <v>7601.026680851135</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6287.148792283407</v>
+        <v>6287.148792283408</v>
       </c>
       <c r="Q71" s="128" t="n">
-        <v>1133.995088438324</v>
+        <v>1133.995088438323</v>
       </c>
       <c r="R71" s="128" t="n">
         <v>364.6164826990977</v>
@@ -24935,7 +24935,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7785.760363420828</v>
+        <v>7785.760363420829</v>
       </c>
       <c r="V71" s="127" t="n">
         <v>6391.704264561599</v>
@@ -25176,19 +25176,19 @@
         <v>828</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7867.39213926166</v>
+        <v>7867.392139261658</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2365.502744595251</v>
+        <v>2365.502744595252</v>
       </c>
       <c r="L75" s="131" t="n">
         <v>540.129599164054</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>90.14648623966944</v>
+        <v>90.14648623966943</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>10863.17096926064</v>
+        <v>10863.17096926063</v>
       </c>
       <c r="P75" s="130" t="n">
         <v>8779.113761857376</v>
@@ -25197,10 +25197,10 @@
         <v>2736.222957408781</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>622.217963822528</v>
+        <v>622.2179638225278</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>97.23255996286009</v>
+        <v>97.23255996286011</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12234.78724305155</v>
@@ -25209,10 +25209,10 @@
         <v>9578.283309154338</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3058.258318549433</v>
+        <v>3058.258318549434</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>690.8187737742181</v>
+        <v>690.8187737742182</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>103.5478408855323</v>
@@ -25444,19 +25444,19 @@
         <v>2351</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>598.5293965081189</v>
+        <v>598.5293965081188</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>24.59313324021368</v>
+        <v>24.59313324021369</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>3.995667682340317</v>
+        <v>3.995667682340316</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>627.1181974306729</v>
+        <v>627.1181974306728</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>740.6706846160412</v>
@@ -25474,7 +25474,7 @@
         <v>804.1565347491608</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>895.7872779917071</v>
+        <v>895.7872779917072</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>77.2441738664258</v>
@@ -25486,7 +25486,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>993.521855931095</v>
+        <v>993.5218559310953</v>
       </c>
     </row>
     <row r="80">
@@ -25614,13 +25614,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>0</v>
+        <v>7.275957614183426e-12</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.88977869013</v>
       </c>
     </row>
     <row r="82">
@@ -25684,10 +25684,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
     </row>
     <row r="83">
@@ -26131,7 +26131,7 @@
         <v>13003.11723008967</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4563.263691598253</v>
+        <v>4563.263691598255</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1187.478837745334</v>
@@ -26262,7 +26262,7 @@
         <v>22311.02510630787</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>21914.20637614638</v>
+        <v>21914.20637614639</v>
       </c>
       <c r="Q91" s="131" t="n">
         <v>1010.723188589527</v>
@@ -26274,10 +26274,10 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>22987.93657739597</v>
+        <v>22987.93657739599</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>22601.76959326364</v>
+        <v>22601.76959326363</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>1056.466494278384</v>
@@ -26289,7 +26289,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>23722.9047948107</v>
+        <v>23722.90479481069</v>
       </c>
     </row>
     <row r="92">
@@ -26384,7 +26384,7 @@
         <v>14559.77935978286</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3657.60118461548</v>
+        <v>3657.601184615481</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>1002.418242930857</v>
@@ -26417,7 +26417,7 @@
         <v>4404.990571608101</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1160.601085888422</v>
+        <v>1160.601085888423</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>239.3114606059943</v>
@@ -26527,7 +26527,7 @@
         <v>3749.971974583752</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>4108.083998434081</v>
+        <v>4108.083998434082</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -26551,13 +26551,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>454.2017636236161</v>
+        <v>454.2017636236162</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4613.53256034453</v>
+        <v>4613.532560344527</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5067.734323968146</v>
+        <v>5067.734323968143</v>
       </c>
     </row>
     <row r="96">
@@ -26655,7 +26655,7 @@
         <v>618.5245169195839</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>209.2035404023792</v>
+        <v>209.2035404023791</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>424.0529667237129</v>
@@ -26664,10 +26664,10 @@
         <v>4168.306998868713</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>3164.707663611443</v>
+        <v>3164.707663611444</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>680.4674119199826</v>
+        <v>680.4674119199829</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>226.5165239898197</v>
@@ -26676,22 +26676,22 @@
         <v>430.5372579133003</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>4502.228857434546</v>
+        <v>4502.228857434547</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>3439.42677325971</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>747.4454037466003</v>
+        <v>747.4454037466005</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>243.6334623001598</v>
+        <v>243.6334623001597</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>443.9492711165447</v>
+        <v>443.9492711165446</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>4874.454910423014</v>
+        <v>4874.454910423015</v>
       </c>
     </row>
     <row r="98">
@@ -26792,10 +26792,10 @@
         <v>169.5275357149585</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>8691.863841275193</v>
+        <v>8691.863841275195</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11742.0153029836</v>
+        <v>11742.01530298361</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>2598.534414052498</v>
@@ -26804,13 +26804,13 @@
         <v>438.2116805097612</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>179.9999157422426</v>
+        <v>179.9999157422499</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>9596.202553104937</v>
+        <v>9596.20255310494</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>12812.94856340944</v>
+        <v>12812.94856340945</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2771.892408298329</v>
@@ -26819,13 +26819,13 @@
         <v>465.1034039087826</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>193.1545602542537</v>
+        <v>193.154560254261</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>10721.53529077529</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>14151.68566323665</v>
+        <v>14151.68566323666</v>
       </c>
     </row>
     <row r="100">
@@ -26874,10 +26874,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>8999.775048831169</v>
+        <v>8999.77504883117</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>8999.775048831169</v>
+        <v>8999.77504883117</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -26889,10 +26889,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>10047.00842355626</v>
+        <v>10047.00842355625</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>10047.00842355626</v>
+        <v>10047.00842355625</v>
       </c>
     </row>
     <row r="101">
@@ -27094,7 +27094,7 @@
         <v>57887.99439294333</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>3115.375739032019</v>
+        <v>3115.375739032018</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>1430266.310556282</v>
@@ -27143,10 +27143,10 @@
         <v>260672.8335634196</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>60611.41979919453</v>
+        <v>60611.41979919454</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>17205.51634726692</v>
+        <v>17205.51634726693</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>1512829.697999806</v>
@@ -27161,7 +27161,7 @@
         <v>61193.9002771325</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>19133.70432187438</v>
+        <v>19133.70432187437</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>1529759.312411638</v>
@@ -28200,7 +28200,7 @@
         <v>69272530.81205237</v>
       </c>
       <c r="AI25" s="46" t="n">
-        <v>82393.1061648711</v>
+        <v>82393.10616487113</v>
       </c>
       <c r="AK25" s="120" t="n">
         <v>1</v>
@@ -28508,7 +28508,7 @@
         <v>17275131.82133583</v>
       </c>
       <c r="AI29" s="56" t="n">
-        <v>1417.428955109499</v>
+        <v>1417.4289551095</v>
       </c>
       <c r="AK29" s="123" t="n">
         <v>5</v>
@@ -28793,7 +28793,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>6744653.252587557</v>
+        <v>6744653.252587556</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>817.5423512722406</v>
@@ -29385,7 +29385,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>2476876.419150953</v>
+        <v>2476876.419150952</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>2448.177946365579</v>
@@ -29465,7 +29465,7 @@
         <v>2260678.222648065</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>2957.226786839574</v>
+        <v>2957.226786839573</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -30019,7 +30019,7 @@
         <v>6715.968437806265</v>
       </c>
       <c r="Q53" s="128" t="n">
-        <v>3429.26860315993</v>
+        <v>3429.268603159931</v>
       </c>
       <c r="R53" s="128" t="n">
         <v>822.8623550462368</v>
@@ -30031,13 +30031,13 @@
         <v>10968.09939601243</v>
       </c>
       <c r="V53" s="127" t="n">
-        <v>6761.020244310002</v>
+        <v>6761.020244310001</v>
       </c>
       <c r="W53" s="128" t="n">
         <v>3491.421839512038</v>
       </c>
       <c r="X53" s="128" t="n">
-        <v>815.5517143006917</v>
+        <v>815.5517143006919</v>
       </c>
       <c r="Y53" s="128" t="n">
         <v>0</v>
@@ -30178,7 +30178,7 @@
         <v>22311.02510630787</v>
       </c>
       <c r="P55" s="130" t="n">
-        <v>21914.20637614638</v>
+        <v>21914.20637614639</v>
       </c>
       <c r="Q55" s="131" t="n">
         <v>1010.723188589527</v>
@@ -30190,10 +30190,10 @@
         <v>0</v>
       </c>
       <c r="T55" s="132" t="n">
-        <v>22987.93657739597</v>
+        <v>22987.93657739599</v>
       </c>
       <c r="V55" s="130" t="n">
-        <v>22601.76959326364</v>
+        <v>22601.76959326363</v>
       </c>
       <c r="W55" s="131" t="n">
         <v>1056.466494278384</v>
@@ -30205,7 +30205,7 @@
         <v>0</v>
       </c>
       <c r="Z55" s="132" t="n">
-        <v>23722.9047948107</v>
+        <v>23722.90479481069</v>
       </c>
       <c r="AE55" s="121" t="n">
         <v>7</v>
@@ -30216,7 +30216,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>5734707.282319223</v>
+        <v>5734707.282319224</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>17549.5900695808</v>
@@ -30325,7 +30325,7 @@
         <v>15561</v>
       </c>
       <c r="J57" s="130" t="n">
-        <v>6692.3872205212</v>
+        <v>6692.387220521201</v>
       </c>
       <c r="K57" s="131" t="n">
         <v>1292.098440020229</v>
@@ -30337,37 +30337,37 @@
         <v>123.8746392546061</v>
       </c>
       <c r="N57" s="132" t="n">
-        <v>8570.648943562837</v>
+        <v>8570.648943562839</v>
       </c>
       <c r="P57" s="130" t="n">
-        <v>6842.391992459443</v>
+        <v>6842.391992459445</v>
       </c>
       <c r="Q57" s="131" t="n">
-        <v>1266.647780097429</v>
+        <v>1266.64778009743</v>
       </c>
       <c r="R57" s="131" t="n">
-        <v>454.6862978521621</v>
+        <v>454.6862978521622</v>
       </c>
       <c r="S57" s="131" t="n">
         <v>127.6595789522098</v>
       </c>
       <c r="T57" s="132" t="n">
-        <v>8691.385649361244</v>
+        <v>8691.385649361247</v>
       </c>
       <c r="V57" s="130" t="n">
-        <v>7242.965830311594</v>
+        <v>7242.965830311593</v>
       </c>
       <c r="W57" s="131" t="n">
-        <v>1346.732253058668</v>
+        <v>1346.732253058667</v>
       </c>
       <c r="X57" s="131" t="n">
-        <v>469.7823121142044</v>
+        <v>469.7823121142043</v>
       </c>
       <c r="Y57" s="131" t="n">
-        <v>135.7636197204621</v>
+        <v>135.763619720462</v>
       </c>
       <c r="Z57" s="132" t="n">
-        <v>9195.244015204929</v>
+        <v>9195.244015204928</v>
       </c>
       <c r="AE57" s="121" t="n">
         <v>9</v>
@@ -30499,7 +30499,7 @@
         <v>3533.802715159584</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>3891.914739009913</v>
+        <v>3891.914739009914</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>0</v>
@@ -30523,13 +30523,13 @@
         <v>0</v>
       </c>
       <c r="X59" s="131" t="n">
-        <v>454.2017636236161</v>
+        <v>454.2017636236162</v>
       </c>
       <c r="Y59" s="131" t="n">
-        <v>4273.42969397765</v>
+        <v>4273.429693977648</v>
       </c>
       <c r="Z59" s="132" t="n">
-        <v>4727.631457601266</v>
+        <v>4727.631457601264</v>
       </c>
       <c r="AE59" s="121" t="n">
         <v>11</v>
@@ -30621,7 +30621,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>1648202.438743795</v>
+        <v>1648202.438743794</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>3969.264717832511</v>
@@ -30655,7 +30655,7 @@
         <v>593.9313836793702</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>205.2078727200389</v>
+        <v>205.2078727200388</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>424.0529667237129</v>
@@ -30664,31 +30664,31 @@
         <v>3541.18880143804</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>2424.036978995402</v>
+        <v>2424.036978995403</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>629.7036766255073</v>
+        <v>629.7036766255076</v>
       </c>
       <c r="R61" s="131" t="n">
-        <v>213.7944091511753</v>
+        <v>213.7944091511754</v>
       </c>
       <c r="S61" s="131" t="n">
         <v>430.5372579133003</v>
       </c>
       <c r="T61" s="132" t="n">
-        <v>3698.072322685386</v>
+        <v>3698.072322685387</v>
       </c>
       <c r="V61" s="130" t="n">
         <v>2543.639495268003</v>
       </c>
       <c r="W61" s="131" t="n">
-        <v>670.2012298801745</v>
+        <v>670.2012298801748</v>
       </c>
       <c r="X61" s="131" t="n">
-        <v>223.1430582271976</v>
+        <v>223.1430582271975</v>
       </c>
       <c r="Y61" s="131" t="n">
-        <v>443.9492711165447</v>
+        <v>443.9492711165446</v>
       </c>
       <c r="Z61" s="132" t="n">
         <v>3880.933054491919</v>
@@ -30811,46 +30811,46 @@
         <v>6312</v>
       </c>
       <c r="J63" s="130" t="n">
-        <v>2455.007697092602</v>
+        <v>2455.007697092595</v>
       </c>
       <c r="K63" s="131" t="n">
         <v>425.6162289008444</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>169.5275357149635</v>
+        <v>169.5275357149644</v>
       </c>
       <c r="M63" s="131" t="n">
-        <v>7231.577856055945</v>
+        <v>7231.577856055947</v>
       </c>
       <c r="N63" s="132" t="n">
-        <v>10281.72931776436</v>
+        <v>10281.72931776435</v>
       </c>
       <c r="P63" s="130" t="n">
-        <v>2598.534414052418</v>
+        <v>2598.534414052403</v>
       </c>
       <c r="Q63" s="131" t="n">
-        <v>438.2116805097858</v>
+        <v>438.211680509783</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>179.9999157422485</v>
+        <v>179.999915742249</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>7996.485702050357</v>
+        <v>7996.48570205036</v>
       </c>
       <c r="T63" s="132" t="n">
-        <v>11213.23171235481</v>
+        <v>11213.23171235479</v>
       </c>
       <c r="V63" s="130" t="n">
-        <v>2771.892408297972</v>
+        <v>2771.892408297979</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>465.1034039087808</v>
+        <v>465.1034039087781</v>
       </c>
       <c r="X63" s="131" t="n">
-        <v>193.1545602542587</v>
+        <v>193.1545602542578</v>
       </c>
       <c r="Y63" s="131" t="n">
-        <v>8980.645512085166</v>
+        <v>8980.645512085162</v>
       </c>
       <c r="Z63" s="132" t="n">
         <v>12410.79588454618</v>
@@ -30916,10 +30916,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>7400.058197776589</v>
+        <v>7400.05819777659</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>7400.058197776589</v>
+        <v>7400.05819777659</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -30931,10 +30931,10 @@
         <v>0</v>
       </c>
       <c r="Y64" s="134" t="n">
-        <v>8306.118644866136</v>
+        <v>8306.118644866132</v>
       </c>
       <c r="Z64" s="135" t="n">
-        <v>8306.118644866136</v>
+        <v>8306.118644866132</v>
       </c>
       <c r="AE64" s="121" t="n">
         <v>16</v>
@@ -31141,37 +31141,37 @@
         <v>0</v>
       </c>
       <c r="J67" s="139" t="n">
-        <v>5930.846562192128</v>
+        <v>5930.846562192127</v>
       </c>
       <c r="K67" s="140" t="n">
         <v>1143.598651544596</v>
       </c>
       <c r="L67" s="140" t="n">
-        <v>553.6881347605801</v>
+        <v>553.6881347605803</v>
       </c>
       <c r="M67" s="140" t="n">
         <v>1456.205310819041</v>
       </c>
       <c r="N67" s="141" t="n">
-        <v>9084.338659316345</v>
+        <v>9084.338659316343</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>5835.383405729967</v>
+        <v>5835.383405729969</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>1154.261197949845</v>
+        <v>1154.261197949846</v>
       </c>
       <c r="R67" s="140" t="n">
-        <v>542.1573693318946</v>
+        <v>542.1573693318948</v>
       </c>
       <c r="S67" s="140" t="n">
         <v>1491.567133808416</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>9023.369106820122</v>
+        <v>9023.369106820126</v>
       </c>
       <c r="V67" s="139" t="n">
-        <v>6328.900915682869</v>
+        <v>6328.900915682868</v>
       </c>
       <c r="W67" s="140" t="n">
         <v>1287.413362242337</v>
@@ -31180,7 +31180,7 @@
         <v>560.4309044370964</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>1679.701399547172</v>
+        <v>1679.701399547171</v>
       </c>
       <c r="Z67" s="141" t="n">
         <v>9856.446581909473</v>
@@ -31222,13 +31222,13 @@
         <v>90613</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>45397.3644152249</v>
+        <v>45397.36441522489</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>7816.344192589595</v>
       </c>
       <c r="L68" s="143" t="n">
-        <v>2645.420721961224</v>
+        <v>2645.420721961225</v>
       </c>
       <c r="M68" s="143" t="n">
         <v>12769.51348801289</v>
@@ -31243,28 +31243,28 @@
         <v>7928.816126932024</v>
       </c>
       <c r="R68" s="143" t="n">
-        <v>2678.021513618306</v>
+        <v>2678.021513618307</v>
       </c>
       <c r="S68" s="143" t="n">
         <v>13934.75040705928</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>78272.16785057605</v>
+        <v>78272.16785057608</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>48250.18848713408</v>
       </c>
       <c r="W68" s="143" t="n">
-        <v>8317.338582880382</v>
+        <v>8317.338582880378</v>
       </c>
       <c r="X68" s="143" t="n">
-        <v>2780.933020225742</v>
+        <v>2780.933020225741</v>
       </c>
       <c r="Y68" s="143" t="n">
         <v>15513.48949644699</v>
       </c>
       <c r="Z68" s="144" t="n">
-        <v>83168.06823155333</v>
+        <v>83168.06823155332</v>
       </c>
       <c r="AE68" s="124" t="n">
         <v>20</v>
@@ -31432,7 +31432,7 @@
         <v>7016</v>
       </c>
       <c r="J71" s="127" t="n">
-        <v>6151.384466191856</v>
+        <v>6151.384466191857</v>
       </c>
       <c r="K71" s="128" t="n">
         <v>1095.863111337395</v>
@@ -31444,13 +31444,13 @@
         <v>0</v>
       </c>
       <c r="N71" s="129" t="n">
-        <v>7601.026680851134</v>
+        <v>7601.026680851135</v>
       </c>
       <c r="P71" s="127" t="n">
-        <v>6287.148792283407</v>
+        <v>6287.148792283408</v>
       </c>
       <c r="Q71" s="128" t="n">
-        <v>1133.995088438324</v>
+        <v>1133.995088438323</v>
       </c>
       <c r="R71" s="128" t="n">
         <v>364.6164826990977</v>
@@ -31459,7 +31459,7 @@
         <v>0</v>
       </c>
       <c r="T71" s="129" t="n">
-        <v>7785.760363420828</v>
+        <v>7785.760363420829</v>
       </c>
       <c r="V71" s="127" t="n">
         <v>6391.704264561599</v>
@@ -31700,19 +31700,19 @@
         <v>828</v>
       </c>
       <c r="J75" s="130" t="n">
-        <v>7867.39213926166</v>
+        <v>7867.392139261658</v>
       </c>
       <c r="K75" s="131" t="n">
-        <v>2365.502744595251</v>
+        <v>2365.502744595252</v>
       </c>
       <c r="L75" s="131" t="n">
         <v>540.129599164054</v>
       </c>
       <c r="M75" s="131" t="n">
-        <v>90.14648623966944</v>
+        <v>90.14648623966943</v>
       </c>
       <c r="N75" s="132" t="n">
-        <v>10863.17096926064</v>
+        <v>10863.17096926063</v>
       </c>
       <c r="P75" s="130" t="n">
         <v>8779.113761857376</v>
@@ -31721,10 +31721,10 @@
         <v>2736.222957408781</v>
       </c>
       <c r="R75" s="131" t="n">
-        <v>622.217963822528</v>
+        <v>622.2179638225278</v>
       </c>
       <c r="S75" s="131" t="n">
-        <v>97.23255996286009</v>
+        <v>97.23255996286011</v>
       </c>
       <c r="T75" s="132" t="n">
         <v>12234.78724305155</v>
@@ -31733,10 +31733,10 @@
         <v>9578.283309154338</v>
       </c>
       <c r="W75" s="131" t="n">
-        <v>3058.258318549433</v>
+        <v>3058.258318549434</v>
       </c>
       <c r="X75" s="131" t="n">
-        <v>690.8187737742181</v>
+        <v>690.8187737742182</v>
       </c>
       <c r="Y75" s="131" t="n">
         <v>103.5478408855323</v>
@@ -31968,19 +31968,19 @@
         <v>2351</v>
       </c>
       <c r="J79" s="130" t="n">
-        <v>598.5293965081189</v>
+        <v>598.5293965081188</v>
       </c>
       <c r="K79" s="131" t="n">
-        <v>24.59313324021368</v>
+        <v>24.59313324021369</v>
       </c>
       <c r="L79" s="131" t="n">
-        <v>3.995667682340317</v>
+        <v>3.995667682340316</v>
       </c>
       <c r="M79" s="131" t="n">
         <v>0</v>
       </c>
       <c r="N79" s="132" t="n">
-        <v>627.1181974306729</v>
+        <v>627.1181974306728</v>
       </c>
       <c r="P79" s="130" t="n">
         <v>740.6706846160412</v>
@@ -31998,7 +31998,7 @@
         <v>804.1565347491608</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>895.7872779917071</v>
+        <v>895.7872779917072</v>
       </c>
       <c r="W79" s="131" t="n">
         <v>77.2441738664258</v>
@@ -32010,7 +32010,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>993.521855931095</v>
+        <v>993.5218559310953</v>
       </c>
     </row>
     <row r="80">
@@ -32138,13 +32138,13 @@
         <v>0</v>
       </c>
       <c r="X81" s="131" t="n">
-        <v>0</v>
+        <v>7.275957614183426e-12</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.88977869013</v>
       </c>
     </row>
     <row r="82">
@@ -32208,10 +32208,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>1740.889778690123</v>
+        <v>1740.889778690122</v>
       </c>
     </row>
     <row r="83">
@@ -32655,7 +32655,7 @@
         <v>13003.11723008967</v>
       </c>
       <c r="Q89" s="128" t="n">
-        <v>4563.263691598253</v>
+        <v>4563.263691598255</v>
       </c>
       <c r="R89" s="128" t="n">
         <v>1187.478837745334</v>
@@ -32786,7 +32786,7 @@
         <v>22311.02510630787</v>
       </c>
       <c r="P91" s="130" t="n">
-        <v>21914.20637614638</v>
+        <v>21914.20637614639</v>
       </c>
       <c r="Q91" s="131" t="n">
         <v>1010.723188589527</v>
@@ -32798,10 +32798,10 @@
         <v>0</v>
       </c>
       <c r="T91" s="132" t="n">
-        <v>22987.93657739597</v>
+        <v>22987.93657739599</v>
       </c>
       <c r="V91" s="130" t="n">
-        <v>22601.76959326364</v>
+        <v>22601.76959326363</v>
       </c>
       <c r="W91" s="131" t="n">
         <v>1056.466494278384</v>
@@ -32813,7 +32813,7 @@
         <v>0</v>
       </c>
       <c r="Z91" s="132" t="n">
-        <v>23722.9047948107</v>
+        <v>23722.90479481069</v>
       </c>
     </row>
     <row r="92">
@@ -32908,7 +32908,7 @@
         <v>14559.77935978286</v>
       </c>
       <c r="K93" s="131" t="n">
-        <v>3657.60118461548</v>
+        <v>3657.601184615481</v>
       </c>
       <c r="L93" s="131" t="n">
         <v>1002.418242930857</v>
@@ -32941,7 +32941,7 @@
         <v>4404.990571608101</v>
       </c>
       <c r="X93" s="131" t="n">
-        <v>1160.601085888422</v>
+        <v>1160.601085888423</v>
       </c>
       <c r="Y93" s="131" t="n">
         <v>239.3114606059943</v>
@@ -33051,7 +33051,7 @@
         <v>3749.971974583752</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>4108.083998434081</v>
+        <v>4108.083998434082</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>0</v>
@@ -33075,13 +33075,13 @@
         <v>0</v>
       </c>
       <c r="X95" s="131" t="n">
-        <v>454.2017636236161</v>
+        <v>454.2017636236162</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>4613.53256034453</v>
+        <v>4613.532560344527</v>
       </c>
       <c r="Z95" s="132" t="n">
-        <v>5067.734323968146</v>
+        <v>5067.734323968143</v>
       </c>
     </row>
     <row r="96">
@@ -33179,7 +33179,7 @@
         <v>618.5245169195839</v>
       </c>
       <c r="L97" s="131" t="n">
-        <v>209.2035404023792</v>
+        <v>209.2035404023791</v>
       </c>
       <c r="M97" s="131" t="n">
         <v>424.0529667237129</v>
@@ -33188,10 +33188,10 @@
         <v>4168.306998868713</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>3164.707663611443</v>
+        <v>3164.707663611444</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>680.4674119199826</v>
+        <v>680.4674119199829</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>226.5165239898197</v>
@@ -33200,22 +33200,22 @@
         <v>430.5372579133003</v>
       </c>
       <c r="T97" s="132" t="n">
-        <v>4502.228857434546</v>
+        <v>4502.228857434547</v>
       </c>
       <c r="V97" s="130" t="n">
         <v>3439.42677325971</v>
       </c>
       <c r="W97" s="131" t="n">
-        <v>747.4454037466003</v>
+        <v>747.4454037466005</v>
       </c>
       <c r="X97" s="131" t="n">
-        <v>243.6334623001598</v>
+        <v>243.6334623001597</v>
       </c>
       <c r="Y97" s="131" t="n">
-        <v>443.9492711165447</v>
+        <v>443.9492711165446</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>4874.454910423014</v>
+        <v>4874.454910423015</v>
       </c>
     </row>
     <row r="98">
@@ -33316,10 +33316,10 @@
         <v>169.5275357149585</v>
       </c>
       <c r="M99" s="131" t="n">
-        <v>8691.863841275193</v>
+        <v>8691.863841275195</v>
       </c>
       <c r="N99" s="132" t="n">
-        <v>11742.0153029836</v>
+        <v>11742.01530298361</v>
       </c>
       <c r="P99" s="130" t="n">
         <v>2598.534414052498</v>
@@ -33328,13 +33328,13 @@
         <v>438.2116805097612</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>179.9999157422426</v>
+        <v>179.9999157422499</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>9596.202553104937</v>
+        <v>9596.20255310494</v>
       </c>
       <c r="T99" s="132" t="n">
-        <v>12812.94856340944</v>
+        <v>12812.94856340945</v>
       </c>
       <c r="V99" s="130" t="n">
         <v>2771.892408298329</v>
@@ -33343,13 +33343,13 @@
         <v>465.1034039087826</v>
       </c>
       <c r="X99" s="131" t="n">
-        <v>193.1545602542537</v>
+        <v>193.154560254261</v>
       </c>
       <c r="Y99" s="131" t="n">
         <v>10721.53529077529</v>
       </c>
       <c r="Z99" s="132" t="n">
-        <v>14151.68566323665</v>
+        <v>14151.68566323666</v>
       </c>
     </row>
     <row r="100">
@@ -33398,10 +33398,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>8999.775048831169</v>
+        <v>8999.77504883117</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>8999.775048831169</v>
+        <v>8999.77504883117</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -33413,10 +33413,10 @@
         <v>0</v>
       </c>
       <c r="Y100" s="134" t="n">
-        <v>10047.00842355626</v>
+        <v>10047.00842355625</v>
       </c>
       <c r="Z100" s="135" t="n">
-        <v>10047.00842355626</v>
+        <v>10047.00842355625</v>
       </c>
     </row>
     <row r="101">
@@ -33618,7 +33618,7 @@
         <v>57887.99439294333</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>3115.375739032019</v>
+        <v>3115.375739032018</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>1430266.310556282</v>
@@ -33667,10 +33667,10 @@
         <v>260672.8335634196</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>60611.41979919453</v>
+        <v>60611.41979919454</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>17205.51634726692</v>
+        <v>17205.51634726693</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>1512829.697999806</v>
@@ -33685,7 +33685,7 @@
         <v>61193.9002771325</v>
       </c>
       <c r="Y104" s="143" t="n">
-        <v>19133.70432187438</v>
+        <v>19133.70432187437</v>
       </c>
       <c r="Z104" s="144" t="n">
         <v>1529759.312411638</v>
